--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_47.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3323584.018036685</v>
+        <v>3316717.025088029</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900007</v>
+        <v>286.4107162898915</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900007</v>
+        <v>286.4107162898915</v>
       </c>
     </row>
     <row r="11">
@@ -672,10 +672,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>127.8837310637179</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1027,13 +1027,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>332.2298619629587</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172409</v>
+        <v>21.95645751172589</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1219,16 +1219,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>300.9629961541975</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>385</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>371.5681244750684</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S11" t="n">
         <v>144.8481678023229</v>
@@ -1447,7 +1447,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.55655664632661</v>
+        <v>274.1550540812894</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1690,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>197.2737972923793</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>144.8481678023229</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X18" t="n">
         <v>69.86273944538755</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>34.55655664632661</v>
+        <v>107.5980768338923</v>
       </c>
       <c r="C21" t="n">
         <v>11.09991244551929</v>
@@ -2167,16 +2167,16 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T23" t="n">
         <v>236.6755817285639</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096178</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2410,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2632,10 +2632,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2683,10 +2683,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U27" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856292</v>
       </c>
       <c r="V27" t="n">
         <v>64.51066719152016</v>
@@ -2802,13 +2802,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H29" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>97.23431917176904</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U32" t="n">
-        <v>299.2212965486107</v>
+        <v>303.1866879340253</v>
       </c>
       <c r="V32" t="n">
         <v>279.8510241668239</v>
@@ -3106,16 +3106,16 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="F33" t="n">
-        <v>62.67776252544254</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3358,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3391,13 +3391,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S36" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T36" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856292</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>97.23431917176916</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178217</v>
       </c>
       <c r="S39" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T39" t="n">
         <v>55.35776521751382</v>
@@ -3750,7 +3750,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H41" t="n">
         <v>58.00965870352741</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>236.6755817285639</v>
@@ -3817,22 +3817,22 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>84.14143263308497</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>284.2120239427945</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4108,7 +4108,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>137.148586410602</v>
       </c>
       <c r="V45" t="n">
         <v>64.51066719152016</v>
@@ -4315,7 +4315,7 @@
         <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4330,16 +4330,16 @@
         <v>30.8</v>
       </c>
       <c r="M2" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="N2" t="n">
-        <v>777.6999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1158.85</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C3" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D3" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E3" t="n">
-        <v>897.189519579215</v>
+        <v>593.1864931608338</v>
       </c>
       <c r="F3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>585.6429020987573</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
         <v>250.1195817084329</v>
@@ -4421,31 +4421,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S3" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>949.9530371097363</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W3" t="n">
-        <v>917.2528927563742</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="4">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>789.9952208079459</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>454.4095016534421</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>439.752262066048</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>50.86337317715914</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>775.7097405151412</v>
+        <v>1247.586867406406</v>
       </c>
       <c r="C7" t="n">
-        <v>901.711746333577</v>
+        <v>1373.588873224842</v>
       </c>
       <c r="D7" t="n">
-        <v>1015.030890458577</v>
+        <v>1486.908017349842</v>
       </c>
       <c r="E7" t="n">
-        <v>1132.85979466999</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="F7" t="n">
-        <v>1257.220767261926</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="G7" t="n">
-        <v>1410.627333148811</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="H7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="I7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="J7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="K7" t="n">
-        <v>1540.000000000001</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="L7" t="n">
         <v>1517.821760089168</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>229.621392885946</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>401.5123111456234</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>552.5431021698168</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>663.9524028488491</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G8" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
@@ -4804,16 +4804,16 @@
         <v>793.0999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>793.1</v>
+        <v>1174.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="O8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="P8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4822,25 +4822,25 @@
         <v>1540</v>
       </c>
       <c r="S8" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T8" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V8" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="C9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
-        <v>554.1226081268142</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
-        <v>554.1226081268142</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S9" t="n">
-        <v>970.2346453614745</v>
+        <v>473.7545795777692</v>
       </c>
       <c r="T9" t="n">
-        <v>964.8227613033797</v>
+        <v>98.43324172416462</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6102766971304</v>
+        <v>98.22075711791538</v>
       </c>
       <c r="V9" t="n">
-        <v>949.9530371097363</v>
+        <v>83.56351753052128</v>
       </c>
       <c r="W9" t="n">
-        <v>917.2528927563742</v>
+        <v>50.86337317715914</v>
       </c>
       <c r="X9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1247.586867406406</v>
+        <v>576.8883476291953</v>
       </c>
       <c r="C10" t="n">
-        <v>1373.588873224842</v>
+        <v>702.8903534476311</v>
       </c>
       <c r="D10" t="n">
-        <v>1486.908017349842</v>
+        <v>816.2094975726312</v>
       </c>
       <c r="E10" t="n">
-        <v>1540</v>
+        <v>934.0384017840443</v>
       </c>
       <c r="F10" t="n">
-        <v>1540</v>
+        <v>1058.39937437598</v>
       </c>
       <c r="G10" t="n">
-        <v>1540</v>
+        <v>1211.805940262865</v>
       </c>
       <c r="H10" t="n">
-        <v>1540</v>
+        <v>1381.322525422263</v>
       </c>
       <c r="I10" t="n">
         <v>1540</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>701.4985197772105</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>873.3894380368879</v>
+        <v>202.6909182596774</v>
       </c>
       <c r="X10" t="n">
-        <v>1024.420229061081</v>
+        <v>353.721709283871</v>
       </c>
       <c r="Y10" t="n">
-        <v>1135.829529740114</v>
+        <v>465.1310099629032</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L11" t="n">
-        <v>618.3311712710653</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M11" t="n">
-        <v>1129.18</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N11" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O11" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
       </c>
       <c r="R11" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
         <v>108.0308712378207</v>
@@ -5099,10 +5099,10 @@
         <v>108.0308712378207</v>
       </c>
       <c r="F12" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G12" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H12" t="n">
         <v>44.72</v>
@@ -5156,7 +5156,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="13">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C13" t="n">
         <v>946.5478354584615</v>
@@ -5220,22 +5220,22 @@
         <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="14">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C14" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D14" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E14" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F14" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5272,22 +5272,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1542.849113037656</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M14" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N14" t="n">
-        <v>2096.259113037656</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T14" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U14" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V14" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W14" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X14" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y14" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
         <v>44.72</v>
@@ -5369,31 +5369,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>601.6825341814942</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>536.5202440890496</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>453.3150492306369</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>382.7466255484273</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>332.8563298250593</v>
       </c>
     </row>
     <row r="16">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
@@ -5509,10 +5509,10 @@
         <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="L17" t="n">
-        <v>690.5809049473327</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M17" t="n">
         <v>690.5809049473327</v>
@@ -5530,28 +5530,28 @@
         <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5624,13 +5624,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>444.3729990826727</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D19" t="n">
         <v>1010.366979583462</v>
@@ -5694,22 +5694,22 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H20" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
@@ -5746,49 +5746,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L20" t="n">
-        <v>618.3311712710653</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M20" t="n">
-        <v>1129.18</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N20" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5798,25 +5798,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.7782575464261</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C21" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D21" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E21" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H21" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I21" t="n">
         <v>44.72</v>
@@ -5931,10 +5931,10 @@
         <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V22" t="n">
         <v>521.9574820108303</v>
@@ -5983,19 +5983,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1243.990904947333</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6004,7 +6004,7 @@
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
         <v>2085.68327354774</v>
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H24" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I24" t="n">
         <v>44.72</v>
@@ -6104,7 +6104,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H25" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J25" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K25" t="n">
         <v>1921.561060958496</v>
@@ -6180,10 +6180,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C26" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D26" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E26" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F26" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G26" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
@@ -6220,19 +6220,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>690.5809049473327</v>
+        <v>1286.552076218397</v>
       </c>
       <c r="M26" t="n">
-        <v>690.5809049473327</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N26" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O26" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>1797.400904947332</v>
@@ -6244,25 +6244,25 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T26" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U26" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V26" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W26" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X26" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y26" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="27">
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C27" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
         <v>44.72</v>
@@ -6326,22 +6326,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6445,10 +6445,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,22 +6457,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>1542.849113037656</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M29" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="N29" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D30" t="n">
         <v>44.72</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C32" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D32" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E32" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G32" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
@@ -6694,22 +6694,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L32" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M32" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.18</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O32" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6724,19 +6724,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V32" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W32" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X32" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y32" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="33">
@@ -6749,13 +6749,13 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C33" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D33" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E33" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F33" t="n">
         <v>44.72</v>
@@ -6825,16 +6825,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C34" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D34" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F34" t="n">
         <v>1153.55685638681</v>
@@ -6885,16 +6885,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W34" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X34" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y34" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="35">
@@ -6937,16 +6937,16 @@
         <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1542.849113037656</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N35" t="n">
-        <v>1542.849113037656</v>
+        <v>2236</v>
       </c>
       <c r="O35" t="n">
-        <v>1542.849113037656</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7034,25 +7034,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7131,7 +7131,7 @@
         <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>137.1709049473328</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K38" t="n">
-        <v>690.5809049473327</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L38" t="n">
-        <v>1243.990904947333</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M38" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="N38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>409.4673863086053</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
         <v>1010.366979583462</v>
@@ -7365,10 +7365,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
         <v>103.3156148520479</v>
@@ -7429,25 +7429,25 @@
         <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7460,19 +7460,19 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E42" t="n">
-        <v>387.7869114524009</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H42" t="n">
         <v>44.72</v>
@@ -7639,25 +7639,25 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>64.92117127106515</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>618.3311712710652</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L44" t="n">
-        <v>1171.741171271065</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M44" t="n">
-        <v>1682.59</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N44" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7742,13 +7742,13 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>913.0695679010663</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>795.3281537953983</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>739.4112192322531</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
         <v>688.6936841209533</v>
@@ -7773,31 +7773,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K46" t="n">
         <v>1921.561060958496</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>913.7065720867618</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>862.2489580698352</v>
@@ -7982,10 +7982,10 @@
         <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8447,10 +8447,10 @@
         <v>385</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>846.6934025142796</v>
+        <v>846.6934025142797</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L11" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,13 +8690,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,25 +8915,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>211.4002806471673</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,13 +9152,13 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
@@ -9389,25 +9389,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,22 +9626,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,22 +9863,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>257.1230221309868</v>
+        <v>300.1141042229713</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="M29" t="n">
-        <v>801.3851497733039</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10346,16 +10346,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>661.3924512348954</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,19 +10580,19 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>257.410082171668</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>128.4277587171436</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
@@ -10817,7 +10817,7 @@
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
@@ -10829,7 +10829,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>55.44822975121676</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11300,10 +11300,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646055104</v>
+        <v>1.591170646053286</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -26290,7 +26290,7 @@
         <v>1479768.022390799</v>
       </c>
       <c r="I2" t="n">
-        <v>1479768.022390798</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="J2" t="n">
         <v>1479768.022390799</v>
@@ -26308,10 +26308,10 @@
         <v>1479768.022390799</v>
       </c>
       <c r="O2" t="n">
-        <v>1479768.022390798</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="P2" t="n">
-        <v>1479768.022390798</v>
+        <v>1479768.022390799</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984991</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>716253.426479071</v>
+        <v>714737.570790755</v>
       </c>
       <c r="C6" t="n">
-        <v>853831.4066128853</v>
+        <v>852315.5509245697</v>
       </c>
       <c r="D6" t="n">
-        <v>855892.1785252014</v>
+        <v>854376.3228368853</v>
       </c>
       <c r="E6" t="n">
-        <v>532014.6191642637</v>
+        <v>530272.7693511561</v>
       </c>
       <c r="F6" t="n">
-        <v>875205.5145097681</v>
+        <v>873463.66469666</v>
       </c>
       <c r="G6" t="n">
-        <v>877151.0909779532</v>
+        <v>875409.2411648456</v>
       </c>
       <c r="H6" t="n">
-        <v>879099.3677952545</v>
+        <v>877357.5179821471</v>
       </c>
       <c r="I6" t="n">
-        <v>881050.3644386145</v>
+        <v>879308.5146255071</v>
       </c>
       <c r="J6" t="n">
-        <v>467484.1006402405</v>
+        <v>465742.2508271324</v>
       </c>
       <c r="K6" t="n">
-        <v>884960.5963924595</v>
+        <v>883218.7465793515</v>
       </c>
       <c r="L6" t="n">
-        <v>886919.8719527186</v>
+        <v>885178.0221396113</v>
       </c>
       <c r="M6" t="n">
-        <v>827633.947848698</v>
+        <v>825892.0980355908</v>
       </c>
       <c r="N6" t="n">
-        <v>890846.8448835517</v>
+        <v>889104.9950704437</v>
       </c>
       <c r="O6" t="n">
-        <v>612814.5841412892</v>
+        <v>611072.7343281821</v>
       </c>
       <c r="P6" t="n">
-        <v>894785.1869922994</v>
+        <v>893043.3371791923</v>
       </c>
     </row>
   </sheetData>
@@ -26999,16 +26999,16 @@
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
@@ -27030,13 +27030,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -27051,19 +27051,19 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -27088,22 +27088,22 @@
         <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27112,10 +27112,10 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>214.7883661581947</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27761,13 +27761,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>139.8182410159025</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,13 +27806,13 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>67.98049779722805</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27837,16 +27837,16 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>334.6091701401496</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>359.450587567467</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
         <v>176.6334556201183</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27998,16 +27998,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>31.20509103222366</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>81.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>33.78964074244533</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28074,19 +28074,19 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>334.6091701401468</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>336.9137329713681</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28116,16 +28116,16 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S11" t="n">
         <v>350</v>
@@ -28226,7 +28226,7 @@
         <v>350</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -28235,13 +28235,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124344</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>269.4903246609786</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28305,7 +28305,7 @@
         <v>350</v>
       </c>
       <c r="C13" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="D13" t="n">
         <v>350</v>
@@ -28356,7 +28356,7 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28469,10 +28469,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>269.6305770343469</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
         <v>350</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28715,10 +28715,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28760,7 +28760,7 @@
         <v>350</v>
       </c>
       <c r="W18" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X18" t="n">
         <v>350</v>
@@ -28782,7 +28782,7 @@
         <v>350</v>
       </c>
       <c r="D19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="C21" t="n">
         <v>350</v>
@@ -28946,16 +28946,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -29067,13 +29067,13 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
       </c>
       <c r="V22" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W22" t="n">
         <v>350</v>
@@ -29140,10 +29140,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T23" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29189,10 +29189,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29240,7 +29240,7 @@
         <v>350</v>
       </c>
       <c r="Y24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29277,7 +29277,7 @@
         <v>350</v>
       </c>
       <c r="K25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L25" t="n">
         <v>350</v>
@@ -29316,7 +29316,7 @@
         <v>350</v>
       </c>
       <c r="X25" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29411,10 +29411,10 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D27" t="n">
-        <v>285.2599243722601</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -29462,10 +29462,10 @@
         <v>350</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -29581,13 +29581,13 @@
         <v>350</v>
       </c>
       <c r="G29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H29" t="n">
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29645,13 +29645,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="C30" t="n">
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722602</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29824,7 +29824,7 @@
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29860,7 +29860,7 @@
         <v>350</v>
       </c>
       <c r="U32" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="V32" t="n">
         <v>350</v>
@@ -29885,16 +29885,16 @@
         <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="F33" t="n">
-        <v>276.9584798124343</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>325.7395358750273</v>
@@ -29973,7 +29973,7 @@
         <v>350</v>
       </c>
       <c r="F34" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G34" t="n">
         <v>350</v>
@@ -30021,7 +30021,7 @@
         <v>350</v>
       </c>
       <c r="V34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="W34" t="n">
         <v>350</v>
@@ -30137,10 +30137,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30170,13 +30170,13 @@
         <v>350</v>
       </c>
       <c r="S36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30267,7 +30267,7 @@
         <v>350</v>
       </c>
       <c r="Y37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
     </row>
     <row r="38">
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30404,10 +30404,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="S39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>350</v>
@@ -30441,7 +30441,7 @@
         <v>350</v>
       </c>
       <c r="D40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="E40" t="n">
         <v>350</v>
@@ -30501,7 +30501,7 @@
         <v>350</v>
       </c>
       <c r="X40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y40" t="n">
         <v>350</v>
@@ -30529,7 +30529,7 @@
         <v>350</v>
       </c>
       <c r="G41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H41" t="n">
         <v>350</v>
@@ -30565,7 +30565,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T41" t="n">
         <v>350</v>
@@ -30596,22 +30596,22 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>262.1624218828912</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>217.1263858913485</v>
@@ -30878,16 +30878,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
+        <v>350</v>
+      </c>
+      <c r="S45" t="n">
+        <v>350</v>
+      </c>
+      <c r="T45" t="n">
+        <v>350</v>
+      </c>
+      <c r="U45" t="n">
         <v>263.0617733495848</v>
-      </c>
-      <c r="S45" t="n">
-        <v>350</v>
-      </c>
-      <c r="T45" t="n">
-        <v>350</v>
-      </c>
-      <c r="U45" t="n">
-        <v>350</v>
       </c>
       <c r="V45" t="n">
         <v>350</v>
@@ -30936,7 +30936,7 @@
         <v>350</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34752,7 +34752,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>369.4444444444444</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>385</v>
@@ -34761,10 +34761,10 @@
         <v>385</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -35123,16 +35123,16 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>53.628265303193</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>130.6794614658484</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35226,10 +35226,10 @@
         <v>385</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N8" t="n">
-        <v>369.4444444444443</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35360,19 +35360,19 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>53.62826530319025</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>160.2802773512498</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,16 +35402,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L11" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,13 +35469,13 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35591,7 +35591,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C13" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608951</v>
       </c>
       <c r="D13" t="n">
         <v>64.46378194444452</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
@@ -35694,25 +35694,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>141.1524110730749</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35931,13 +35931,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
@@ -36068,7 +36068,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D19" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E19" t="n">
         <v>69.01909516304346</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36168,25 +36168,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,13 +36353,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V22" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W22" t="n">
         <v>123.6271901612903</v>
@@ -36405,22 +36405,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N23" t="n">
         <v>559</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36563,7 +36563,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K25" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36602,7 +36602,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X25" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y25" t="n">
         <v>62.53464715053764</v>
@@ -36642,22 +36642,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>257.1230221309868</v>
+        <v>300.1141042229713</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>184.1434931650601</v>
+      </c>
+      <c r="M29" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N29" t="n">
         <v>559</v>
       </c>
-      <c r="L29" t="n">
+      <c r="O29" t="n">
         <v>559</v>
       </c>
-      <c r="M29" t="n">
-        <v>257.1230221309866</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37125,16 +37125,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>184.1434931650601</v>
+        <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37259,7 +37259,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G34" t="n">
         <v>104.95612715847</v>
@@ -37307,7 +37307,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V34" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W34" t="n">
         <v>123.6271901612903</v>
@@ -37359,19 +37359,19 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>257.1230221309866</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37553,7 +37553,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467183</v>
       </c>
     </row>
     <row r="38">
@@ -37587,7 +37587,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>93.38475247205329</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
@@ -37596,7 +37596,7 @@
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
@@ -37608,7 +37608,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37727,7 +37727,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>69.01909516304346</v>
@@ -37787,7 +37787,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y40" t="n">
         <v>62.53464715053764</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>20.40522350612643</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38222,7 +38222,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
